--- a/EG2B.xlsx
+++ b/EG2B.xlsx
@@ -136,94 +136,94 @@
     <t>LFEBUOY REF LIME 650</t>
   </si>
   <si>
+    <t>20026207</t>
+  </si>
+  <si>
+    <t>CIPTADENT MX.COM 190</t>
+  </si>
+  <si>
+    <t>RT,(E-3B)</t>
+  </si>
+  <si>
+    <t>20141837</t>
+  </si>
+  <si>
+    <t>PEPSODENT PG FIFA95</t>
+  </si>
+  <si>
+    <t>20142282</t>
+  </si>
+  <si>
+    <t>CLOSEUP PG FIFA 95G</t>
+  </si>
+  <si>
+    <t>20141838</t>
+  </si>
+  <si>
+    <t>PEPSODENT SG FIFA 1S</t>
+  </si>
+  <si>
+    <t>20136584</t>
+  </si>
+  <si>
+    <t>HMLAYA DS TRM.SRM 15</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>20139313</t>
+  </si>
+  <si>
+    <t>HMLY PRFY N/C SM 30</t>
+  </si>
+  <si>
+    <t>20139950</t>
+  </si>
+  <si>
+    <t>HMLY TURMERIC CSM 30</t>
+  </si>
+  <si>
+    <t>20114051</t>
+  </si>
+  <si>
+    <t>H&amp;S SHP A.GTL 160 ML</t>
+  </si>
+  <si>
+    <t>20106953</t>
+  </si>
+  <si>
+    <t>H&amp;S SHP A.APK 160 ML</t>
+  </si>
+  <si>
+    <t>20140791</t>
+  </si>
+  <si>
+    <t>DOVE BIOTIN SHP 150</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>20138900</t>
+  </si>
+  <si>
+    <t>SNSLK SH AD 160 ML</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
     <t>20028002</t>
   </si>
   <si>
     <t>LFEBUOY SHP S&amp;SH 340</t>
   </si>
   <si>
+    <t>8</t>
+  </si>
+  <si>
     <t>PT,(E-4B)</t>
-  </si>
-  <si>
-    <t>20138900</t>
-  </si>
-  <si>
-    <t>SNSLK SHP AD</t>
-  </si>
-  <si>
-    <t>20140791</t>
-  </si>
-  <si>
-    <t>DOVE BIOTIN SHP 150</t>
-  </si>
-  <si>
-    <t>20141837</t>
-  </si>
-  <si>
-    <t>PEPSODENT PG FIFA95</t>
-  </si>
-  <si>
-    <t>20142282</t>
-  </si>
-  <si>
-    <t>CLOSEUP PG FIFA 95G</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>20026207</t>
-  </si>
-  <si>
-    <t>CIPTADENT MX.COM 190</t>
-  </si>
-  <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>RT,(E-3B)</t>
-  </si>
-  <si>
-    <t>20141838</t>
-  </si>
-  <si>
-    <t>PEPSODENT SG FIFA 1S</t>
-  </si>
-  <si>
-    <t>7</t>
-  </si>
-  <si>
-    <t>20136584</t>
-  </si>
-  <si>
-    <t>HMLAYA DS TRM.SRM 15</t>
-  </si>
-  <si>
-    <t>20139313</t>
-  </si>
-  <si>
-    <t>HMLY PRFY N/C SM 30</t>
-  </si>
-  <si>
-    <t>TG,(E-3B)</t>
-  </si>
-  <si>
-    <t>20139950</t>
-  </si>
-  <si>
-    <t>HMLY TURMERIC CSM 30</t>
-  </si>
-  <si>
-    <t>20136390</t>
-  </si>
-  <si>
-    <t>VSLNE LOT DW RDNC100</t>
-  </si>
-  <si>
-    <t>20136394</t>
-  </si>
-  <si>
-    <t>VSLNE LOT OVR RDN100</t>
   </si>
 </sst>
 </file>
@@ -1003,7 +1003,7 @@
         <v>8</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>9</v>
+        <v>36</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
@@ -1023,7 +1023,7 @@
         <v>12</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>9</v>
+        <v>36</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
@@ -1057,13 +1057,13 @@
         <v>3</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>27</v>
+        <v>52</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>52</v>
+        <v>4</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>36</v>
+        <v>43</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
@@ -1077,41 +1077,41 @@
         <v>3</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>27</v>
+        <v>52</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>55</v>
+        <v>8</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>56</v>
+        <v>43</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>27</v>
+        <v>52</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>59</v>
+        <v>12</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>36</v>
+        <v>43</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>3</v>
@@ -1120,18 +1120,18 @@
         <v>52</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>4</v>
+        <v>27</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>56</v>
+        <v>9</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="C26" s="1" t="s">
         <v>3</v>
@@ -1140,18 +1140,18 @@
         <v>52</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>8</v>
+        <v>52</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>64</v>
+        <v>9</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="C27" s="1" t="s">
         <v>3</v>
@@ -1160,18 +1160,18 @@
         <v>52</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>12</v>
+        <v>63</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>64</v>
+        <v>9</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="C28" s="1" t="s">
         <v>3</v>
@@ -1180,7 +1180,7 @@
         <v>52</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>27</v>
+        <v>66</v>
       </c>
       <c r="F28" s="1" t="s">
         <v>9</v>
@@ -1188,10 +1188,10 @@
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C29" s="1" t="s">
         <v>3</v>
@@ -1200,10 +1200,10 @@
         <v>52</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>52</v>
+        <v>69</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>9</v>
+        <v>70</v>
       </c>
     </row>
   </sheetData>

--- a/EG2B.xlsx
+++ b/EG2B.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="174" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="204" uniqueCount="87">
   <si>
     <t/>
   </si>
@@ -28,112 +28,163 @@
     <t>1</t>
   </si>
   <si>
+    <t>3</t>
+  </si>
+  <si>
     <t>PT</t>
   </si>
   <si>
-    <t>20090847</t>
-  </si>
-  <si>
-    <t>CERTAINTY POPOK 8S/M</t>
+    <t>20134081</t>
+  </si>
+  <si>
+    <t>IDM CLMAX BRIEF M 2S</t>
   </si>
   <si>
     <t>2</t>
   </si>
   <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>20134082</t>
+  </si>
+  <si>
+    <t>IDM CLMAX BRIEF L 2S</t>
+  </si>
+  <si>
+    <t>20134083</t>
+  </si>
+  <si>
+    <t>IDM CLMAX BRIEF XL2S</t>
+  </si>
+  <si>
+    <t>20134078</t>
+  </si>
+  <si>
+    <t>IDM BOXER PRIA MAX M</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>20134079</t>
+  </si>
+  <si>
+    <t>IDM BOXER PRIA MAX L</t>
+  </si>
+  <si>
+    <t>20134080</t>
+  </si>
+  <si>
+    <t>IDM BXER PRIA MAX XL</t>
+  </si>
+  <si>
+    <t>20136272</t>
+  </si>
+  <si>
+    <t>IDM KAOS CLMAX HTM/M</t>
+  </si>
+  <si>
+    <t>20136273</t>
+  </si>
+  <si>
+    <t>IDM KAOS CLMAX HTM/L</t>
+  </si>
+  <si>
+    <t>20136274</t>
+  </si>
+  <si>
+    <t>IDM KAOS CLMX HTM/XL</t>
+  </si>
+  <si>
+    <t>20136584</t>
+  </si>
+  <si>
+    <t>HMLAYA DS TRM.SRM 15</t>
+  </si>
+  <si>
+    <t>RT,(E-3B)</t>
+  </si>
+  <si>
+    <t>20139313</t>
+  </si>
+  <si>
+    <t>HMLY PRFY N/C SM 30</t>
+  </si>
+  <si>
+    <t>20139950</t>
+  </si>
+  <si>
+    <t>HMLY TURMERIC CSM 30</t>
+  </si>
+  <si>
+    <t>20114051</t>
+  </si>
+  <si>
+    <t>H&amp;S SHP ANTI GTAL145</t>
+  </si>
+  <si>
     <t>PT,(E-3B)</t>
   </si>
   <si>
-    <t>20090848</t>
-  </si>
-  <si>
-    <t>CERTAINTY POPOK 7S/L</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>20134081</t>
-  </si>
-  <si>
-    <t>IDM CLMAX BRIEF M 2S</t>
-  </si>
-  <si>
-    <t>20134082</t>
-  </si>
-  <si>
-    <t>IDM CLMAX BRIEF L 2S</t>
-  </si>
-  <si>
-    <t>20134083</t>
-  </si>
-  <si>
-    <t>IDM CLMAX BRIEF XL2S</t>
-  </si>
-  <si>
-    <t>20134078</t>
-  </si>
-  <si>
-    <t>IDM BOXER PRIA MAX M</t>
-  </si>
-  <si>
-    <t>20134079</t>
-  </si>
-  <si>
-    <t>IDM BOXER PRIA MAX L</t>
-  </si>
-  <si>
-    <t>20134080</t>
-  </si>
-  <si>
-    <t>IDM BXER PRIA MAX XL</t>
-  </si>
-  <si>
-    <t>20136272</t>
-  </si>
-  <si>
-    <t>IDM KAOS CLMAX HTM/M</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>20136273</t>
-  </si>
-  <si>
-    <t>IDM KAOS CLMAX HTM/L</t>
-  </si>
-  <si>
-    <t>20136274</t>
-  </si>
-  <si>
-    <t>IDM KAOS CLMX HTM/XL</t>
-  </si>
-  <si>
-    <t>20141637</t>
-  </si>
-  <si>
-    <t>LIFEBUOY BW FIFA 85G</t>
-  </si>
-  <si>
-    <t>20141446</t>
-  </si>
-  <si>
-    <t>LFBUOY BW FIFA 360G</t>
+    <t>20106953</t>
+  </si>
+  <si>
+    <t>H&amp;S SHP A.APK 160 ML</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>20140791</t>
+  </si>
+  <si>
+    <t>DOVE BIOTIN SHP 150</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>20138900</t>
+  </si>
+  <si>
+    <t>SNSLK SH AD 160 ML</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>20028002</t>
+  </si>
+  <si>
+    <t>LFEBUOY SHP S&amp;SH 340</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
+    <t>PT,(E-4B)</t>
+  </si>
+  <si>
+    <t>20141838</t>
+  </si>
+  <si>
+    <t>PEPSODENT SG FIFA 1S</t>
+  </si>
+  <si>
+    <t>10</t>
   </si>
   <si>
     <t>PT,(E-1B)</t>
   </si>
   <si>
-    <t>20141638</t>
-  </si>
-  <si>
-    <t>LIFEBUOY BW FIFA 500</t>
-  </si>
-  <si>
-    <t>20128374</t>
-  </si>
-  <si>
-    <t>LFEBUOY REF LIME 650</t>
+    <t>20141837</t>
+  </si>
+  <si>
+    <t>PEPSODENT PG FIFA95</t>
+  </si>
+  <si>
+    <t>11</t>
   </si>
   <si>
     <t>20026207</t>
@@ -142,88 +193,85 @@
     <t>CIPTADENT MX.COM 190</t>
   </si>
   <si>
-    <t>RT,(E-3B)</t>
-  </si>
-  <si>
-    <t>20141837</t>
-  </si>
-  <si>
-    <t>PEPSODENT PG FIFA95</t>
-  </si>
-  <si>
-    <t>20142282</t>
-  </si>
-  <si>
-    <t>CLOSEUP PG FIFA 95G</t>
-  </si>
-  <si>
-    <t>20141838</t>
-  </si>
-  <si>
-    <t>PEPSODENT SG FIFA 1S</t>
-  </si>
-  <si>
-    <t>20136584</t>
-  </si>
-  <si>
-    <t>HMLAYA DS TRM.SRM 15</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>20139313</t>
-  </si>
-  <si>
-    <t>HMLY PRFY N/C SM 30</t>
-  </si>
-  <si>
-    <t>20139950</t>
-  </si>
-  <si>
-    <t>HMLY TURMERIC CSM 30</t>
-  </si>
-  <si>
-    <t>20114051</t>
-  </si>
-  <si>
-    <t>H&amp;S SHP A.GTL 160 ML</t>
-  </si>
-  <si>
-    <t>20106953</t>
-  </si>
-  <si>
-    <t>H&amp;S SHP A.APK 160 ML</t>
-  </si>
-  <si>
-    <t>20140791</t>
-  </si>
-  <si>
-    <t>DOVE BIOTIN SHP 150</t>
-  </si>
-  <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>20138900</t>
-  </si>
-  <si>
-    <t>SNSLK SH AD 160 ML</t>
-  </si>
-  <si>
-    <t>7</t>
-  </si>
-  <si>
-    <t>20028002</t>
-  </si>
-  <si>
-    <t>LFEBUOY SHP S&amp;SH 340</t>
-  </si>
-  <si>
-    <t>8</t>
-  </si>
-  <si>
-    <t>PT,(E-4B)</t>
+    <t>12</t>
+  </si>
+  <si>
+    <t>20138647</t>
+  </si>
+  <si>
+    <t>SUN KARA TPK 110ML</t>
+  </si>
+  <si>
+    <t>RT,(E-2B)</t>
+  </si>
+  <si>
+    <t>20128247</t>
+  </si>
+  <si>
+    <t>WNHAE FRIED ROSE 97G</t>
+  </si>
+  <si>
+    <t>10023790</t>
+  </si>
+  <si>
+    <t>SEDAAP MIE A/BW 70 G</t>
+  </si>
+  <si>
+    <t>RT,(E-1B)</t>
+  </si>
+  <si>
+    <t>10023791</t>
+  </si>
+  <si>
+    <t>SEDAAP MIE KR/A 72 G</t>
+  </si>
+  <si>
+    <t>20114755</t>
+  </si>
+  <si>
+    <t>SEDAAP MI S/LKS 83 G</t>
+  </si>
+  <si>
+    <t>20055496</t>
+  </si>
+  <si>
+    <t>PRO CHIZ SPRD 160G</t>
+  </si>
+  <si>
+    <t>20066050</t>
+  </si>
+  <si>
+    <t>DELMONTE SPG.SAUS250</t>
+  </si>
+  <si>
+    <t>20066052</t>
+  </si>
+  <si>
+    <t>DLMONTE BBQ.SAUS 250</t>
+  </si>
+  <si>
+    <t>20009269</t>
+  </si>
+  <si>
+    <t>DELMONTE EXT.HOT 135</t>
+  </si>
+  <si>
+    <t>20142668</t>
+  </si>
+  <si>
+    <t>SAORI SS YAKINIKU133</t>
+  </si>
+  <si>
+    <t>20045611</t>
+  </si>
+  <si>
+    <t>SEDAAP MI GRNG CUP85</t>
+  </si>
+  <si>
+    <t>20099297</t>
+  </si>
+  <si>
+    <t>SDAAP MIE SP.CHKN 81</t>
   </si>
 </sst>
 </file>
@@ -616,13 +664,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F29"/>
+  <dimension ref="A1:F34"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="5" width="3" customWidth="1"/>
+    <col min="4" max="4" width="3" customWidth="1"/>
+    <col min="5" max="5" width="4" customWidth="1"/>
     <col min="6" max="6" width="11" customWidth="1"/>
   </cols>
   <sheetData>
@@ -660,50 +709,50 @@
         <v>4</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F3" s="1" t="s">
         <v>6</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E4" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B4" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>12</v>
-      </c>
       <c r="F4" s="1" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
@@ -717,13 +766,13 @@
         <v>3</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
@@ -737,113 +786,113 @@
         <v>3</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
@@ -857,353 +906,453 @@
         <v>3</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>27</v>
+        <v>9</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>5</v>
+        <v>30</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F13" s="1" t="s">
         <v>30</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D13" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E13" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="F13" s="1" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="F16" s="1" t="s">
         <v>37</v>
-      </c>
-      <c r="B16" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="C16" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D16" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="E16" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F16" s="1" t="s">
-        <v>9</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>27</v>
+        <v>43</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>5</v>
+        <v>37</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>27</v>
+        <v>5</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>4</v>
+        <v>46</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>27</v>
+        <v>5</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>8</v>
+        <v>49</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>36</v>
+        <v>50</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>27</v>
+        <v>5</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>12</v>
+        <v>53</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>36</v>
+        <v>54</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>27</v>
+        <v>5</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>27</v>
+        <v>57</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>36</v>
+        <v>54</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>51</v>
+        <v>59</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>52</v>
+        <v>5</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>4</v>
+        <v>60</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>43</v>
+        <v>30</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>52</v>
+        <v>10</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>43</v>
+        <v>63</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>55</v>
+        <v>64</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>56</v>
+        <v>65</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>52</v>
+        <v>10</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>43</v>
+        <v>63</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>57</v>
+        <v>66</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>58</v>
+        <v>67</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>52</v>
+        <v>10</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>27</v>
+        <v>5</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>9</v>
+        <v>68</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>59</v>
+        <v>69</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="C26" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>52</v>
+        <v>10</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>52</v>
+        <v>10</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>9</v>
+        <v>68</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>62</v>
+        <v>72</v>
       </c>
       <c r="C27" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>52</v>
+        <v>10</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>63</v>
+        <v>17</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>9</v>
+        <v>68</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
-        <v>64</v>
+        <v>73</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>65</v>
+        <v>74</v>
       </c>
       <c r="C28" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>52</v>
+        <v>17</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>66</v>
+        <v>4</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>9</v>
+        <v>68</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
-        <v>67</v>
+        <v>75</v>
       </c>
       <c r="B29" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D29" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E29" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F29" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A30" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D30" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E30" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F30" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A31" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D31" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E31" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F31" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A32" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D32" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E32" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F32" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="C29" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D29" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="E29" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="F29" s="1" t="s">
-        <v>70</v>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A33" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D33" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E33" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="F33" s="1" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A34" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D34" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E34" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="F34" s="1" t="s">
+        <v>68</v>
       </c>
     </row>
   </sheetData>

--- a/EG2B.xlsx
+++ b/EG2B.xlsx
@@ -11,15 +11,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="204" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="270" uniqueCount="106">
   <si>
     <t/>
   </si>
   <si>
-    <t>20071123</t>
-  </si>
-  <si>
-    <t>IDM JAS HUJAN SETLN</t>
+    <t>20011007</t>
+  </si>
+  <si>
+    <t>LFBUOY BW M.CARE 380</t>
   </si>
   <si>
     <t>EG2B</t>
@@ -31,21 +31,108 @@
     <t>3</t>
   </si>
   <si>
+    <t>PT,(E-3B)</t>
+  </si>
+  <si>
+    <t>20011008</t>
+  </si>
+  <si>
+    <t>LIFEBUOY BW RED 380</t>
+  </si>
+  <si>
+    <t>20040217</t>
+  </si>
+  <si>
+    <t>LFBUOY BW C.FRSH 380</t>
+  </si>
+  <si>
+    <t>20041399</t>
+  </si>
+  <si>
+    <t>LIFEBUOY BW LMN 380</t>
+  </si>
+  <si>
+    <t>20049919</t>
+  </si>
+  <si>
+    <t>LUX BW SOFT ROSE 380</t>
+  </si>
+  <si>
+    <t>20049941</t>
+  </si>
+  <si>
+    <t>LUX BW MCG ORCHD 400</t>
+  </si>
+  <si>
+    <t>20122042</t>
+  </si>
+  <si>
+    <t>LUX BW HJB Z&amp;MD 400</t>
+  </si>
+  <si>
+    <t>20128374</t>
+  </si>
+  <si>
+    <t>LFEBUOY REF LIME 650</t>
+  </si>
+  <si>
     <t>PT</t>
   </si>
   <si>
+    <t>20121373</t>
+  </si>
+  <si>
+    <t>SPR PELL AB CTRS 500</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>20135247</t>
+  </si>
+  <si>
+    <t>BAYGON FLRL.FNTSY500</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>RT,(E-3.5B)</t>
+  </si>
+  <si>
+    <t>20135248</t>
+  </si>
+  <si>
+    <t>BAYGON CHRRY BRRY500</t>
+  </si>
+  <si>
+    <t>20134078</t>
+  </si>
+  <si>
+    <t>IDM BOXER PRIA MAX M</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>20134079</t>
+  </si>
+  <si>
+    <t>IDM BOXER PRIA MAX L</t>
+  </si>
+  <si>
+    <t>20134080</t>
+  </si>
+  <si>
+    <t>IDM BXER PRIA MAX XL</t>
+  </si>
+  <si>
     <t>20134081</t>
   </si>
   <si>
     <t>IDM CLMAX BRIEF M 2S</t>
   </si>
   <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
     <t>20134082</t>
   </si>
   <si>
@@ -58,27 +145,6 @@
     <t>IDM CLMAX BRIEF XL2S</t>
   </si>
   <si>
-    <t>20134078</t>
-  </si>
-  <si>
-    <t>IDM BOXER PRIA MAX M</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>20134079</t>
-  </si>
-  <si>
-    <t>IDM BOXER PRIA MAX L</t>
-  </si>
-  <si>
-    <t>20134080</t>
-  </si>
-  <si>
-    <t>IDM BXER PRIA MAX XL</t>
-  </si>
-  <si>
     <t>20136272</t>
   </si>
   <si>
@@ -97,103 +163,100 @@
     <t>IDM KAOS CLMX HTM/XL</t>
   </si>
   <si>
-    <t>20136584</t>
-  </si>
-  <si>
-    <t>HMLAYA DS TRM.SRM 15</t>
+    <t>20106953</t>
+  </si>
+  <si>
+    <t>H&amp;S SHP A.APK 160 ML</t>
+  </si>
+  <si>
+    <t>20114051</t>
+  </si>
+  <si>
+    <t>H&amp;S SHP ANTI GTAL145</t>
+  </si>
+  <si>
+    <t>20140791</t>
+  </si>
+  <si>
+    <t>DOVE BIOTIN SHP 150</t>
+  </si>
+  <si>
+    <t>20138900</t>
+  </si>
+  <si>
+    <t>SNSLK SH AD 160 ML</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>20028002</t>
+  </si>
+  <si>
+    <t>LFEBUOY SHP S&amp;SH 340</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>PT,(E-4B)</t>
+  </si>
+  <si>
+    <t>20130519</t>
+  </si>
+  <si>
+    <t>SDP MI AYM NMPOL 75G</t>
+  </si>
+  <si>
+    <t>RT,(E-1B)</t>
+  </si>
+  <si>
+    <t>20136091</t>
+  </si>
+  <si>
+    <t>NESTLE TRIX PCK 60G</t>
+  </si>
+  <si>
+    <t>20125633</t>
+  </si>
+  <si>
+    <t>ABC GL AREN PCK 9'S</t>
+  </si>
+  <si>
+    <t>20141838</t>
+  </si>
+  <si>
+    <t>PEPSODENT SG FIFA 1S</t>
+  </si>
+  <si>
+    <t>PT,(E-1B)</t>
+  </si>
+  <si>
+    <t>20141837</t>
+  </si>
+  <si>
+    <t>PEPSODENT PG FIFA95</t>
+  </si>
+  <si>
+    <t>20026207</t>
+  </si>
+  <si>
+    <t>CIPTADENT MX.COM 190</t>
   </si>
   <si>
     <t>RT,(E-3B)</t>
   </si>
   <si>
-    <t>20139313</t>
-  </si>
-  <si>
-    <t>HMLY PRFY N/C SM 30</t>
-  </si>
-  <si>
-    <t>20139950</t>
-  </si>
-  <si>
-    <t>HMLY TURMERIC CSM 30</t>
-  </si>
-  <si>
-    <t>20114051</t>
-  </si>
-  <si>
-    <t>H&amp;S SHP ANTI GTAL145</t>
-  </si>
-  <si>
-    <t>PT,(E-3B)</t>
-  </si>
-  <si>
-    <t>20106953</t>
-  </si>
-  <si>
-    <t>H&amp;S SHP A.APK 160 ML</t>
-  </si>
-  <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>20140791</t>
-  </si>
-  <si>
-    <t>DOVE BIOTIN SHP 150</t>
-  </si>
-  <si>
-    <t>7</t>
-  </si>
-  <si>
-    <t>20138900</t>
-  </si>
-  <si>
-    <t>SNSLK SH AD 160 ML</t>
+    <t>20133740</t>
+  </si>
+  <si>
+    <t>T/O BRIGHTNG.MOIST50</t>
   </si>
   <si>
     <t>8</t>
   </si>
   <si>
-    <t>20028002</t>
-  </si>
-  <si>
-    <t>LFEBUOY SHP S&amp;SH 340</t>
-  </si>
-  <si>
-    <t>9</t>
-  </si>
-  <si>
-    <t>PT,(E-4B)</t>
-  </si>
-  <si>
-    <t>20141838</t>
-  </si>
-  <si>
-    <t>PEPSODENT SG FIFA 1S</t>
-  </si>
-  <si>
-    <t>10</t>
-  </si>
-  <si>
-    <t>PT,(E-1B)</t>
-  </si>
-  <si>
-    <t>20141837</t>
-  </si>
-  <si>
-    <t>PEPSODENT PG FIFA95</t>
-  </si>
-  <si>
-    <t>11</t>
-  </si>
-  <si>
-    <t>20026207</t>
-  </si>
-  <si>
-    <t>CIPTADENT MX.COM 190</t>
-  </si>
-  <si>
-    <t>12</t>
+    <t>RT,(E-2B)</t>
   </si>
   <si>
     <t>20138647</t>
@@ -202,9 +265,6 @@
     <t>SUN KARA TPK 110ML</t>
   </si>
   <si>
-    <t>RT,(E-2B)</t>
-  </si>
-  <si>
     <t>20128247</t>
   </si>
   <si>
@@ -215,9 +275,6 @@
   </si>
   <si>
     <t>SEDAAP MIE A/BW 70 G</t>
-  </si>
-  <si>
-    <t>RT,(E-1B)</t>
   </si>
   <si>
     <t>10023791</t>
@@ -664,15 +721,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F34"/>
+  <dimension ref="A1:F45"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="3" customWidth="1"/>
-    <col min="5" max="5" width="4" customWidth="1"/>
-    <col min="6" max="6" width="11" customWidth="1"/>
+    <col min="4" max="5" width="3" customWidth="1"/>
+    <col min="6" max="6" width="13" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -726,10 +782,10 @@
         <v>3</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F3" s="1" t="s">
         <v>6</v>
@@ -737,19 +793,19 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F4" s="1" t="s">
         <v>6</v>
@@ -757,19 +813,19 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F5" s="1" t="s">
         <v>6</v>
@@ -777,19 +833,19 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="F6" s="1" t="s">
         <v>6</v>
@@ -797,19 +853,19 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="F7" s="1" t="s">
         <v>6</v>
@@ -817,19 +873,19 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="F8" s="1" t="s">
         <v>6</v>
@@ -837,82 +893,82 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>6</v>
+        <v>21</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E10" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="B10" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="E10" s="1" t="s">
-        <v>17</v>
-      </c>
       <c r="F10" s="1" t="s">
-        <v>6</v>
+        <v>21</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B11" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="B11" s="1" t="s">
+      <c r="C11" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E11" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="C11" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="E11" s="1" t="s">
-        <v>17</v>
-      </c>
       <c r="F11" s="1" t="s">
-        <v>6</v>
+        <v>28</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F12" s="1" t="s">
         <v>28</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D12" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="E12" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F12" s="1" t="s">
-        <v>30</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
@@ -926,53 +982,53 @@
         <v>3</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>5</v>
+        <v>33</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>5</v>
+        <v>33</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>5</v>
+        <v>33</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>10</v>
+        <v>33</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>5</v>
+        <v>33</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>37</v>
+        <v>21</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
@@ -986,373 +1042,593 @@
         <v>3</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>5</v>
+        <v>33</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>37</v>
+        <v>21</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B17" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="B17" s="1" t="s">
-        <v>42</v>
-      </c>
       <c r="C17" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>5</v>
+        <v>33</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>37</v>
+        <v>21</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>5</v>
+        <v>33</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>46</v>
+        <v>33</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>37</v>
+        <v>21</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>5</v>
+        <v>33</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>49</v>
+        <v>5</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>50</v>
+        <v>21</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>5</v>
+        <v>33</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>53</v>
+        <v>5</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>54</v>
+        <v>21</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>5</v>
+        <v>33</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>57</v>
+        <v>5</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>54</v>
+        <v>21</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>59</v>
+        <v>51</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>5</v>
+        <v>33</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>60</v>
+        <v>24</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>30</v>
+        <v>6</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>61</v>
+        <v>52</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>62</v>
+        <v>53</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>10</v>
+        <v>33</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>63</v>
+        <v>6</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>10</v>
+        <v>33</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>9</v>
+        <v>27</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>63</v>
+        <v>6</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>67</v>
+        <v>57</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>10</v>
+        <v>33</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>5</v>
+        <v>58</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>68</v>
+        <v>6</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="C26" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>10</v>
+        <v>33</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>10</v>
+        <v>61</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="C27" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="C28" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="C29" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>30</v>
+        <v>65</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
       <c r="C30" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>5</v>
+        <v>27</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>30</v>
+        <v>72</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="C31" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>10</v>
+        <v>58</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>30</v>
+        <v>72</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="C32" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>17</v>
+        <v>61</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>68</v>
+        <v>77</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="C33" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>68</v>
+        <v>81</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D34" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E34" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F34" s="1" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A35" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="B35" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="B34" s="1" t="s">
+      <c r="C35" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D35" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E35" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="F35" s="1" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A36" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="C34" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D34" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="E34" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="F34" s="1" t="s">
-        <v>68</v>
+      <c r="B36" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D36" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E36" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F36" s="1" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A37" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D37" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E37" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F37" s="1" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A38" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D38" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E38" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F38" s="1" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A39" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D39" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E39" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F39" s="1" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A40" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="C40" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D40" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E40" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="F40" s="1" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A41" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="C41" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D41" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E41" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F41" s="1" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A42" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="C42" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D42" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E42" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F42" s="1" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A43" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="C43" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D43" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E43" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F43" s="1" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A44" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="B44" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="C44" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D44" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E44" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="F44" s="1" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A45" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="C45" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D45" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E45" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="F45" s="1" t="s">
+        <v>65</v>
       </c>
     </row>
   </sheetData>
